--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project wittawat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD2252E9-E975-4812-A550-73A8B1DEC828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3ED4D0-10FD-4A35-B9CF-5944EBE2C836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D83949F6-E965-4507-AEDE-3C9312BAE01F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
   <si>
     <t>Module</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t xml:space="preserve">High </t>
+  </si>
+  <si>
+    <t>ระบบปฏิเสธการเข้าถึง (Access Denied / 403) หรือบังคับเด้งไปหน้าแรก</t>
   </si>
 </sst>
 </file>
@@ -727,7 +730,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -753,7 +756,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
@@ -779,7 +782,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -805,7 +808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
@@ -847,7 +850,9 @@
       <c r="E6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="G6" s="3" t="s">
         <v>80</v>
       </c>

--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project wittawat\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Wittawut\test-cases\member-test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3ED4D0-10FD-4A35-B9CF-5944EBE2C836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A5AC20-07D3-47EF-9E33-E4FF7276717D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D83949F6-E965-4507-AEDE-3C9312BAE01F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="105">
   <si>
     <t>Module</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>Excepted Result</t>
-  </si>
-  <si>
-    <t>Priority</t>
   </si>
   <si>
     <t>1. ไปที่หน้า Login
@@ -286,20 +283,100 @@
     <t>Fail</t>
   </si>
   <si>
-    <t>Critical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High </t>
-  </si>
-  <si>
     <t>ระบบปฏิเสธการเข้าถึง (Access Denied / 403) หรือบังคับเด้งไปหน้าแรก</t>
+  </si>
+  <si>
+    <t>Member</t>
+  </si>
+  <si>
+    <t>บันทึกสำเร็จ สมาชิกใหม่พร้อมใช้งาน</t>
+  </si>
+  <si>
+    <t>1. เข้าเมนูเพิ่มสมาชิก
+2. กรอกข้อมูลครบถ้วน เลือกประเภท Student (M006)</t>
+  </si>
+  <si>
+    <t>Add Member Fail (Duplicate Code)</t>
+  </si>
+  <si>
+    <t>Add Member (Student</t>
+  </si>
+  <si>
+    <t>Add Member Fail (Missing Req)</t>
+  </si>
+  <si>
+    <t>Login by Librarian / Admin</t>
+  </si>
+  <si>
+    <t>ระบบมี M001 อยู่แล้ว</t>
+  </si>
+  <si>
+    <t>ระบบแสดง Error “รหัสสมาชิกนี้มีในระบบแล้ว” บันทึกไม่สำเร็จ</t>
+  </si>
+  <si>
+    <t>1. เมนูเพิ่มสมาชิก
+2. กรอกรหัส แต่ไม่ได้กรอก “ชื่อ-สกุล”
+3. กด Save</t>
+  </si>
+  <si>
+    <t>ระบบแสดง Error ป้องกันไม่ให้ลงข้อมูลในฐานข้อมูล</t>
+  </si>
+  <si>
+    <t>Edit Member Detail</t>
+  </si>
+  <si>
+    <t>Delete Member (Safe)</t>
+  </si>
+  <si>
+    <t>Delete Member (Has Active Borrow)</t>
+  </si>
+  <si>
+    <t>View Member Dashboard</t>
+  </si>
+  <si>
+    <t>Member M002 มีอยู่จริง</t>
+  </si>
+  <si>
+    <t>สมาชิกไม่มียืม/ยอดค้าง</t>
+  </si>
+  <si>
+    <t>สมาชิกกำลังยืมหนังสืออยู่</t>
+  </si>
+  <si>
+    <t>1. เข้าเมนูค้นหา/แก้ไชสมาชิก
+2. เลือก M002
+3. แก้ไขข้อมูลบางฟิลด์แล้ว Save</t>
+  </si>
+  <si>
+    <t>1. เลือกสมาชิกล่าสุดที่เพิ่งสร้าง
+2. กดลบ</t>
+  </si>
+  <si>
+    <t>1. เลือกสมาชิกที่ยังคืนหนังสือไม่ครบ
+2. กดลบ</t>
+  </si>
+  <si>
+    <t>1. ค้นหา M001
+2. เข้าหน้า Profile</t>
+  </si>
+  <si>
+    <t>ข้อมูลของ M002 ถูกอัปเดตในระบบถูกต้อง</t>
+  </si>
+  <si>
+    <t>สมาชิกถูกลบออกจากระบบ (หรือ Deactivated)</t>
+  </si>
+  <si>
+    <t>ไม่อนุญาตให้ลบ แสดงแจ้งเตือน “สมาชิกรายนี้ยังมีหนังสือค้างยืม”</t>
+  </si>
+  <si>
+    <t>แสดงสถานะประเภทสมาชิก, ยอดคงเหลือในการยืม, รายการหนังสือที่ยืมอยู่</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,13 +386,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF373D49"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -341,25 +411,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -375,7 +443,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ธีมของ Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -691,724 +759,743 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE52615-FB70-4F85-80C5-12E473692F08}">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="77" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" customWidth="1"/>
+    <col min="5" max="5" width="53.28515625" customWidth="1"/>
+    <col min="6" max="6" width="79.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="F2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G3" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="C7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="2"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
+      <c r="G52" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Wittawut\test-cases\member-test-cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Wittawut\test-cases\book-test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A5AC20-07D3-47EF-9E33-E4FF7276717D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5D4910-0957-40F8-A23A-68BDB2644639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D83949F6-E965-4507-AEDE-3C9312BAE01F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="136">
   <si>
     <t>Module</t>
   </si>
@@ -370,13 +370,108 @@
   </si>
   <si>
     <t>แสดงสถานะประเภทสมาชิก, ยอดคงเหลือในการยืม, รายการหนังสือที่ยืมอยู่</t>
+  </si>
+  <si>
+    <t>Book</t>
+  </si>
+  <si>
+    <t>Add Book Success</t>
+  </si>
+  <si>
+    <t>Add Book Fail (Dup ISBN)</t>
+  </si>
+  <si>
+    <t>Edit Quantity</t>
+  </si>
+  <si>
+    <t>Delete Book (No History)</t>
+  </si>
+  <si>
+    <t>Delete Book (Being Borrowed)</t>
+  </si>
+  <si>
+    <t>Real-time Status Display</t>
+  </si>
+  <si>
+    <t>Upload Book Artwork</t>
+  </si>
+  <si>
+    <t>Create Categories</t>
+  </si>
+  <si>
+    <t>ISBN นี้มีบันทึกแล้ว</t>
+  </si>
+  <si>
+    <t>หนังสือมี Stock=3</t>
+  </si>
+  <si>
+    <t>หนังสือว่าง ไม่มีใครยืม</t>
+  </si>
+  <si>
+    <t>หนังสือถูกยืมอยู่</t>
+  </si>
+  <si>
+    <t>โททัลจำนวนมี 3 เล่ม ถูกยืม 1</t>
+  </si>
+  <si>
+    <t>เตรียมไฟล์ .JPG</t>
+  </si>
+  <si>
+    <t>1. สร้างข้อมููลหนังสือใส่ Title, Author, จำนวน 5 เล่ม</t>
+  </si>
+  <si>
+    <t>1. กรอกข้อมูลและตั้งค่า ISBN เดิม</t>
+  </si>
+  <si>
+    <t>1. เข้าไปปรับจำนวนจาก 3 เป็น 10</t>
+  </si>
+  <si>
+    <t>บันทึกสำเร็จ และสถานะคือ “Available = 5”</t>
+  </si>
+  <si>
+    <t>แสดงข้อผิดพลาด ISBN ซ้ำซ้อน</t>
+  </si>
+  <si>
+    <t>Stock ในระบบเปลี่ยนเป็น 10 สามารถให้ยืมเพิ่มได้</t>
+  </si>
+  <si>
+    <t>1. กด Delete ตำราที่ไม่มีประวัติ</t>
+  </si>
+  <si>
+    <t>ลบสำเร็จและหายไปจากรายการ</t>
+  </si>
+  <si>
+    <t>1. เลือกลบรายการที่ขึ้นสถานะ Borrowed</t>
+  </si>
+  <si>
+    <t>ไม่อนุญาตให้ลบ / ป้องกัน Referential Integrity Error ในฐานข้อมูล</t>
+  </si>
+  <si>
+    <t>1. เช็คหน้า Catalog</t>
+  </si>
+  <si>
+    <t>แสดงผล “Total=3, Available=2” ทันที</t>
+  </si>
+  <si>
+    <t>1. เพิ่ม/แก้ไขหนังสือ แนบหน้าปก
+2. Save</t>
+  </si>
+  <si>
+    <t>ภาพแสดงขึ้นมาที่หน้ารายการหนังสือถูกต้อง ไม่เพี้ยน</t>
+  </si>
+  <si>
+    <t>1. เข้า Setting &gt; Category
+2. เพิ่ม “Fiction”</t>
+  </si>
+  <si>
+    <t>หมวดหมู่ถูกเพิ่ม นำไปผูกตอนสร้าง Book List ได้</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,6 +485,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -399,7 +506,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -407,23 +514,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE8E8E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE8E8E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE8E8E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE8E8E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -762,740 +903,836 @@
   <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" customWidth="1"/>
-    <col min="5" max="5" width="53.28515625" customWidth="1"/>
-    <col min="6" max="6" width="79.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="8" style="4" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="53.28515625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="79.28515625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="8" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="8" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="2"/>
+      <c r="B14" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B15" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B16" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B17" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B18" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="B19" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="B20" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="2"/>
+      <c r="B21" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="2"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="8"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="2"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="8"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="2"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="8"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="2"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="8"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="2"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="8"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="2"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="8"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="2"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="8"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="2"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="8"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="2"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="8"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="2"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="8"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="2"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="8"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="2"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="8"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="2"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="8"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="2"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="8"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="2"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="8"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="2"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="2"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="8"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="2"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="8"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="2"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="8"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="2"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="8"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="2"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="8"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="2"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="8"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="2"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="8"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="2"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="8"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="2"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="8"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="2"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="8"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="2"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="8"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="2"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="8"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="2"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="8"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="2"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="8"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
+      <c r="D52" s="2"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
-      <c r="G52" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Wittawut\test-cases\book-test-cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Wittawut\test-cases\borrow-test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5D4910-0957-40F8-A23A-68BDB2644639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C62987-A66F-44A3-9A04-C5E8835FCC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D83949F6-E965-4507-AEDE-3C9312BAE01F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="175">
   <si>
     <t>Module</t>
   </si>
@@ -465,13 +465,142 @@
   </si>
   <si>
     <t>หมวดหมู่ถูกเพิ่ม นำไปผูกตอนสร้าง Book List ได้</t>
+  </si>
+  <si>
+    <t>Borrow</t>
+  </si>
+  <si>
+    <t>Student Borrow 1 Book</t>
+  </si>
+  <si>
+    <t>M001 (Student) มีโควต้า</t>
+  </si>
+  <si>
+    <t>1. ทำรายการให้ M001 ยืมหนังสือ 1 เล่ม</t>
+  </si>
+  <si>
+    <t>ยืมผ่าน, โควต้าถูกใช้งานไป 1, Due Date คือ วันนี้ + 14 วัน</t>
+  </si>
+  <si>
+    <t>Teacher Borrow 1 Book</t>
+  </si>
+  <si>
+    <t>M003 (Teacher) มีโควต้า</t>
+  </si>
+  <si>
+    <t>1. ทำรายการให้ M003 ยืมหนังสือ 1 เล่ม</t>
+  </si>
+  <si>
+    <t>Public Borrow 1 Book</t>
+  </si>
+  <si>
+    <t>M004 (Public) มีโควต้า</t>
+  </si>
+  <si>
+    <t>1. ทำรายการให้ M004 ยืมหนังสือ 1 เล่ม</t>
+  </si>
+  <si>
+    <t>ยืมผ่าน, โควต้าถูกใช้งานไป 1, Due Date คือ วันนี้ + 7 วัน</t>
+  </si>
+  <si>
+    <t>Student Max Limit Block</t>
+  </si>
+  <si>
+    <t>Student ยืมครบ 3 เล่มแล้ว</t>
+  </si>
+  <si>
+    <t>1. พยายามทำรายการยืมให้ M001 ในเล่มที่ 4</t>
+  </si>
+  <si>
+    <t>ระบบ Reject แจ้ง “โควต้าเต็ม (ยืมได้สูงสุด 3 เล่ม)”</t>
+  </si>
+  <si>
+    <t>Teacher Max Limit Block</t>
+  </si>
+  <si>
+    <t>Teacher ยืมครบ 5 เล่มแล้ว</t>
+  </si>
+  <si>
+    <t>1. พยายามยืมเล่มที่ 6 ให้ M003</t>
+  </si>
+  <si>
+    <t>ระบบ Reject ยืมไม่ได้</t>
+  </si>
+  <si>
+    <t>Public Max Limit Block</t>
+  </si>
+  <si>
+    <t>Public ยืมครบ 2 เล่มแล้ว</t>
+  </si>
+  <si>
+    <t>1. พยายามยืมเล่มที่ 3 ให้ M004</t>
+  </si>
+  <si>
+    <t>Invalid Member Input</t>
+  </si>
+  <si>
+    <t>1. กรอก Member Code เป็น “XYZ999”</t>
+  </si>
+  <si>
+    <t>Alert แจ้งไม่พบผู้ใช้ในระบบ</t>
+  </si>
+  <si>
+    <t>Borrow Out of Stock Book</t>
+  </si>
+  <si>
+    <t>หนังสือ Available = 0</t>
+  </si>
+  <si>
+    <t>1. ทำรายการยืมหนังสือที่ไม่มีในสต็อก</t>
+  </si>
+  <si>
+    <t>ระบบไม่อนุญาตการยืมเพราะ Stock เป็นศูนย์</t>
+  </si>
+  <si>
+    <t>Consecutive Borrow</t>
+  </si>
+  <si>
+    <t>Student ขอยืมรวด 2 เล่ม</t>
+  </si>
+  <si>
+    <t>1. ทำรายการยืม 2 เล่มต่อเนื่องใน transaction เดียว/บิลเดียว</t>
+  </si>
+  <si>
+    <t>ยืมสำเร็จทั้งคู่ ระบบตัดสต็อกลง 2 อัปเดตโควต้าผู้ใช้ถูกต้อง</t>
+  </si>
+  <si>
+    <t>Block borrow on Fine</t>
+  </si>
+  <si>
+    <t>สมาชิกมียอดค่าปรับค้างชำระ</t>
+  </si>
+  <si>
+    <t>1. สมาชิกจ่ายค่าปรับไม่ครบและพยายามยืมหนังสือใหม่</t>
+  </si>
+  <si>
+    <t>ระบบบล็อค “กรุณาชำระค่าปรับให้ครบก่อนดำเนินการต่อ”</t>
+  </si>
+  <si>
+    <r>
+      <t>ยืมผ่าน, โควต้าถูกใช้งานไป 1, Due Date คือ </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>วันนี้ + 30 วัน</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,6 +621,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <name val="Aptos Display"/>
       <family val="2"/>
@@ -533,23 +669,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -557,14 +683,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -900,839 +1026,951 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE52615-FB70-4F85-80C5-12E473692F08}">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="4" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="53.28515625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="79.28515625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="8" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="53.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="79.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="G21" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+      <c r="G21" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="8"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="B22" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="8"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="B23" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="8"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="B24" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="8"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+      <c r="B25" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="8"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="B26" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="8"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="B27" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="8"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="B28" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="8"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+      <c r="B29" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="8"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="B30" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="8"/>
+      <c r="B31" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="8"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="4"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="8"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="4"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="8"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="4"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="8"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="4"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="8"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="4"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="8"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="8"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="4"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="8"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="4"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="8"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="4"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="8"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="4"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="8"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="4"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="8"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="4"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="8"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="4"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="8"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="4"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="8"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="4"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="8"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="4"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="8"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="4"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="8"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="4"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="8"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="4"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="8"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Wittawut\test-cases\borrow-test-cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Wittawut\test-cases\return-test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C62987-A66F-44A3-9A04-C5E8835FCC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B06A260-E682-4C7E-AD77-9DA05EE06068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D83949F6-E965-4507-AEDE-3C9312BAE01F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="203">
   <si>
     <t>Module</t>
   </si>
@@ -595,12 +595,96 @@
       <t>วันนี้ + 30 วัน</t>
     </r>
   </si>
+  <si>
+    <t>Return</t>
+  </si>
+  <si>
+    <t>Fine</t>
+  </si>
+  <si>
+    <t>Return Before/On Due Date</t>
+  </si>
+  <si>
+    <t>วันที่คืน &lt;= Due Date</t>
+  </si>
+  <si>
+    <t>1. วันนี้ไม่เกินกำหนด สแกน Book ID คืน</t>
+  </si>
+  <si>
+    <t>คืนสำเร็จ ได้หนังสือกลับ Stock 1 โควต้าคนยืมว่าง 1 ไม่เกิดค่าปรับ</t>
+  </si>
+  <si>
+    <t>Return Late by 1 Day</t>
+  </si>
+  <si>
+    <t>วันที่คืน = Due Date + 1 วัน</t>
+  </si>
+  <si>
+    <t>1. เปลี่ยนวันที่จำลอง/ยืมล่วงหน้าไว้ แล้วทำเรื่องคืนช้า 1 วัน</t>
+  </si>
+  <si>
+    <t>คืนได้ แจ้งยอดค่าปรับ 5 บาท ระบบบันทึกหนี้ให้ผู้ยืม</t>
+  </si>
+  <si>
+    <t>Return Late by 5 Days</t>
+  </si>
+  <si>
+    <t>วันที่คืน = Due Date + 5 วัน</t>
+  </si>
+  <si>
+    <t>1. คืนล่าช้า 5 วัน</t>
+  </si>
+  <si>
+    <t>ระบบต้องคำนวณออกยอดค่าปรับ = 25 บาท</t>
+  </si>
+  <si>
+    <t>Check Fine Accumulation</t>
+  </si>
+  <si>
+    <t>1. เข้าดูโปรไฟล์ M001 หรือหน้ารับชำระที่ M001 เป็นเจ้าของ</t>
+  </si>
+  <si>
+    <t>โชว์ประวัติและผลรวมค่าปรับ 25 บาท ที่ค้างอยู่</t>
+  </si>
+  <si>
+    <t>Pay Fine Completely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	ค้างปรับ 25 บาท</t>
+  </si>
+  <si>
+    <t>1. บรรณารักษ์กดคลิก “รับชำระ” แล้วลงยอดชำระ 25 บาท</t>
+  </si>
+  <si>
+    <t>หนี้กลายเป็น 0 สมาชิกกลับมายืมหนังสือได้</t>
+  </si>
+  <si>
+    <t>Return Unborrowed Book</t>
+  </si>
+  <si>
+    <t>Book ID ไม่ถูกยืมอยู่</t>
+  </si>
+  <si>
+    <t>1. พยายามเอาเล่ม Available อยู่แล้วมากดคืน</t>
+  </si>
+  <si>
+    <t>ระบบฟ้อง Error: “ไม่พบประวัติการยืมของหนังสือเล่มนี้”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Lost Book Handler</t>
+  </si>
+  <si>
+    <t>1. Member แจ้งหนังสือหายในตอนทำเรื่องคืน (Damaged/Lost)</t>
+  </si>
+  <si>
+    <t>ปรับเงิน 200 บาท (ค่าปรับ Max Limit/หรือตามราคาหนังสือ) และปรับสถานะเป็น Lost</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -610,12 +694,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -669,7 +747,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -677,19 +755,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1040,937 +1112,943 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+      <c r="G31" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+      <c r="B32" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="4"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+      <c r="B33" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="4"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="B34" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="4"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="B35" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="4"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+      <c r="B36" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="4"/>
+      <c r="B37" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="4"/>
+      <c r="B38" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="4"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="4"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="4"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="4"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="G43" s="4"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="4"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="4"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="4"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="4"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="4"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="4"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="4"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Wittawut\test-cases\return-test-cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\not99\Downloads\test-cases\test-cases\Search &amp; Browse-test-cases -\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B06A260-E682-4C7E-AD77-9DA05EE06068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CE10FC-B8C0-4694-91D2-C8876315CDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D83949F6-E965-4507-AEDE-3C9312BAE01F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="216">
   <si>
     <t>Module</t>
   </si>
@@ -678,6 +678,45 @@
   </si>
   <si>
     <t>ปรับเงิน 200 บาท (ค่าปรับ Max Limit/หรือตามราคาหนังสือ) และปรับสถานะเป็น Lost</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Exact Search</t>
+  </si>
+  <si>
+    <t>1. ช่องค้นหา ป้อน “การเขียนโปรแกรม Python” สมบูรณ์</t>
+  </si>
+  <si>
+    <t>โชว์ Book Detail ขึ้นมาอย่างถูกต้องตรงตัว</t>
+  </si>
+  <si>
+    <t>Keyword / Partial Search</t>
+  </si>
+  <si>
+    <t>1. ช่องค้นหา ป้อนคำว่า “ข้อมูล”</t>
+  </si>
+  <si>
+    <t>แสดงผลหนังสือที่มีคำว่าข้อมูลในชื่อ เช่น “โครงสร้างข้อมูล”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Search No Match</t>
+  </si>
+  <si>
+    <t>Search By Author / ISBN</t>
+  </si>
+  <si>
+    <t>1. ช่องค้นหา ป้อน “เอเลี่ยนบุกโลก”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	ระบบไม่พัง แสดงข้อความสุภาพ “No items match your search”</t>
+  </si>
+  <si>
+    <t>1. ป้อนชื่อผู้แต่งแทนชื่อเรื่อง</t>
+  </si>
+  <si>
+    <t>สามารถ Return ค่าตารางของหนังสือเล่มนั้นได้เช่นกัน</t>
   </si>
 </sst>
 </file>
@@ -766,7 +805,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -782,7 +821,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ธีมของ Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1985,24 +2024,96 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>67</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">

--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\not99\Downloads\test-cases\test-cases\Search &amp; Browse-test-cases -\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\not99\Downloads\test-cases\test-cases\System Limits &amp; Vulnerability-test-cases - - Copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CE10FC-B8C0-4694-91D2-C8876315CDA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632D00DE-745E-43F3-AB1D-DB66ECA5A9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D83949F6-E965-4507-AEDE-3C9312BAE01F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="234">
   <si>
     <t>Module</t>
   </si>
@@ -718,12 +718,86 @@
   <si>
     <t>สามารถ Return ค่าตารางของหนังสือเล่มนั้นได้เช่นกัน</t>
   </si>
+  <si>
+    <t>Limit</t>
+  </si>
+  <si>
+    <t>Sec.</t>
+  </si>
+  <si>
+    <t>Concur.</t>
+  </si>
+  <si>
+    <t>UI/UX</t>
+  </si>
+  <si>
+    <t>Max Overdue Cap (BR-007)</t>
+  </si>
+  <si>
+    <t>เลยกำหนดมาร่วม 1 ปี</t>
+  </si>
+  <si>
+    <t>1. ทำการคืนหนังสือที่เลยกำหนดมา 365 วัน (ควรเสีย 365*5 = 1,825 บาท)</t>
+  </si>
+  <si>
+    <t>ระบบคิดค่าปรับตันอยู่ที่ Max Limit 200 บาท (ตามเอกสาร SRS BR-007)</t>
+  </si>
+  <si>
+    <t>SQL Injection on Search</t>
+  </si>
+  <si>
+    <t>ระบบ Safe แสดงแค่ผลลัพธ์ว่าไม่เจอ ไม่ดั๊มป์หรือพ่น Database Scheme</t>
+  </si>
+  <si>
+    <t>Double Borrow Attack</t>
+  </si>
+  <si>
+    <t>Book: 1 , User: 2 คน</t>
+  </si>
+  <si>
+    <t>1. เปิดสิทธิ์ให้คน 2 คนกดยืมหนังสือเล่มเดียวที่เหลือแค่ 1 เล่ม พร้อม ๆ กัน</t>
+  </si>
+  <si>
+    <t>คนที่คลิกคนแรกได้ไป, รายการที่ 2 ต้องโดน Reject แบบ Transaction Safe</t>
+  </si>
+  <si>
+    <t>Responsiveness Check</t>
+  </si>
+  <si>
+    <t>1. ย่อขนาดหน้าต่างเบราว์เซอร์ให้เท่าจอ Mobile (375px)</t>
+  </si>
+  <si>
+    <t>ตารางไม่เละ เมนูหดเป็น Hamburger มองเห็นได้ครบ</t>
+  </si>
+  <si>
+    <r>
+      <t>1. พิมพ์ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>' OR 1=1--</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t> ในช่องค้นหาและเอนเทอร์</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -746,6 +820,12 @@
     <font>
       <i/>
       <sz val="11"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="9.9"/>
       <name val="Aptos Display"/>
       <family val="2"/>
       <scheme val="major"/>
@@ -1140,13 +1220,13 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="34.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="53.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="79.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="65.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="77.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
@@ -1840,7 +1920,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>56</v>
       </c>
@@ -2116,24 +2196,96 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>71</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">

--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\not99\Downloads\test-cases\test-cases\System Limits &amp; Vulnerability-test-cases - - Copy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\not99\Downloads\test-cases\test-cases\Automation, QA-test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632D00DE-745E-43F3-AB1D-DB66ECA5A9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E1FD57-6173-4510-9733-FA31EE82622F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D83949F6-E965-4507-AEDE-3C9312BAE01F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="258">
   <si>
     <t>Module</t>
   </si>
@@ -791,6 +791,78 @@
       </rPr>
       <t> ในช่องค้นหาและเอนเทอร์</t>
     </r>
+  </si>
+  <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Auto.</t>
+  </si>
+  <si>
+    <t>Visual</t>
+  </si>
+  <si>
+    <t>Perf.</t>
+  </si>
+  <si>
+    <t>Auto.</t>
+  </si>
+  <si>
+    <t>Black Box &amp; Exploratory</t>
+  </si>
+  <si>
+    <t>Environment ปกติ</t>
+  </si>
+  <si>
+    <t>1. Manual Tester ทำการทดสอบโดยทดลอง input แปลกๆ และสุ่มกดเมนูต่างๆ</t>
+  </si>
+  <si>
+    <t>ตรวจพบ Edge Cases และ Bug ใหม่ๆ, สรุปผลทดสอบลงรายงาน</t>
+  </si>
+  <si>
+    <t>Playwright Tests (E2E)</t>
+  </si>
+  <si>
+    <t>เตรียม Playwright Script</t>
+  </si>
+  <si>
+    <t>1. Automation Engineer รันคำสั่งทดสอบ E2E Flow ของระบบทั้งหมด</t>
+  </si>
+  <si>
+    <t>Script รันผ่านสำเร็จ มี Test Report แจ้งผล Pass/Fail อัตโนมัติ</t>
+  </si>
+  <si>
+    <t>Visual &amp; Cross-browser</t>
+  </si>
+  <si>
+    <t>1. QA Analyst ตรวจสอบ UI บน Chrome, Edge, Safari และ Firefox</t>
+  </si>
+  <si>
+    <t>Components, สี, การจัดวางแสดงผลตรงตาม Design ไม่ผิดเพี้ยน</t>
+  </si>
+  <si>
+    <t>Load Testing (100 Users)</t>
+  </si>
+  <si>
+    <t>1. จำลองผู้ใช้งาน 100 คนค้นหาหนังสือและยืมคืนพร้อมกัน (อ้างอิง NFR 4.1)</t>
+  </si>
+  <si>
+    <t>ระบบทำงานได้ปกติ Response Time โดยเฉลี่ยไม่เกิน 2-3 วินาที</t>
+  </si>
+  <si>
+    <t>Backup / Failover Check</t>
+  </si>
+  <si>
+    <t>มีสิทธิ์เข้าถึงฝั่ง Server Docker</t>
+  </si>
+  <si>
+    <t>1. สั่ง Backup ฐานข้อมูล และจำลอง Database Crash (ปิด Container)</t>
+  </si>
+  <si>
+    <t>ข้อมูลกลับมาได้ครบถ้วนจากการกู้คืน ภายใน 4 ชม. ตาม NFR</t>
+  </si>
+  <si>
+    <t>ใช้เครื่องมือเช่น k6</t>
   </si>
 </sst>
 </file>
@@ -866,7 +938,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -883,6 +955,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1224,7 +1297,7 @@
     <col min="2" max="2" width="8.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="65.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="67.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="77.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="2"/>
@@ -2288,29 +2361,119 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B49" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B50" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>76</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\not99\Downloads\test-cases\test-cases\Automation, QA-test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E1FD57-6173-4510-9733-FA31EE82622F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8DD40D-1F5E-41AE-9301-F99B78D7096D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D83949F6-E965-4507-AEDE-3C9312BAE01F}"/>
   </bookViews>
@@ -2411,7 +2411,7 @@
       <c r="A49" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="2" t="s">
         <v>236</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -2434,7 +2434,7 @@
       <c r="A50" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="5" t="s">
         <v>237</v>
       </c>
       <c r="C50" s="5" t="s">

--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\not99\Downloads\test-cases\test-cases\Automation, QA-test-cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project wittawat\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8DD40D-1F5E-41AE-9301-F99B78D7096D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4139EF25-A52C-4562-82CF-5AC4CAFC5941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D83949F6-E965-4507-AEDE-3C9312BAE01F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="252">
   <si>
     <t>Module</t>
   </si>
@@ -793,76 +793,58 @@
     </r>
   </si>
   <si>
-    <t>Manual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	Auto.</t>
-  </si>
-  <si>
-    <t>Visual</t>
-  </si>
-  <si>
-    <t>Perf.</t>
-  </si>
-  <si>
-    <t>Auto.</t>
-  </si>
-  <si>
-    <t>Black Box &amp; Exploratory</t>
-  </si>
-  <si>
-    <t>Environment ปกติ</t>
-  </si>
-  <si>
-    <t>1. Manual Tester ทำการทดสอบโดยทดลอง input แปลกๆ และสุ่มกดเมนูต่างๆ</t>
-  </si>
-  <si>
-    <t>ตรวจพบ Edge Cases และ Bug ใหม่ๆ, สรุปผลทดสอบลงรายงาน</t>
-  </si>
-  <si>
-    <t>Playwright Tests (E2E)</t>
-  </si>
-  <si>
-    <t>เตรียม Playwright Script</t>
-  </si>
-  <si>
-    <t>1. Automation Engineer รันคำสั่งทดสอบ E2E Flow ของระบบทั้งหมด</t>
-  </si>
-  <si>
-    <t>Script รันผ่านสำเร็จ มี Test Report แจ้งผล Pass/Fail อัตโนมัติ</t>
-  </si>
-  <si>
-    <t>Visual &amp; Cross-browser</t>
-  </si>
-  <si>
-    <t>1. QA Analyst ตรวจสอบ UI บน Chrome, Edge, Safari และ Firefox</t>
-  </si>
-  <si>
-    <t>Components, สี, การจัดวางแสดงผลตรงตาม Design ไม่ผิดเพี้ยน</t>
-  </si>
-  <si>
-    <t>Load Testing (100 Users)</t>
-  </si>
-  <si>
-    <t>1. จำลองผู้ใช้งาน 100 คนค้นหาหนังสือและยืมคืนพร้อมกัน (อ้างอิง NFR 4.1)</t>
-  </si>
-  <si>
-    <t>ระบบทำงานได้ปกติ Response Time โดยเฉลี่ยไม่เกิน 2-3 วินาที</t>
-  </si>
-  <si>
-    <t>Backup / Failover Check</t>
-  </si>
-  <si>
-    <t>มีสิทธิ์เข้าถึงฝั่ง Server Docker</t>
-  </si>
-  <si>
-    <t>1. สั่ง Backup ฐานข้อมูล และจำลอง Database Crash (ปิด Container)</t>
-  </si>
-  <si>
-    <t>ข้อมูลกลับมาได้ครบถ้วนจากการกู้คืน ภายใน 4 ชม. ตาม NFR</t>
-  </si>
-  <si>
-    <t>ใช้เครื่องมือเช่น k6</t>
+    <t>Toast Alert &amp; Feedback</t>
+  </si>
+  <si>
+    <t>1. ทำรายการไม่สำเร็จ เช่น คีย์รหัสหนังสือผิด</t>
+  </si>
+  <si>
+    <t>มุมจอแสดง Notification Popup แจ้ง Error สั้นๆ แล้วหายไป</t>
+  </si>
+  <si>
+    <t>Button Loading State</t>
+  </si>
+  <si>
+    <t>กดปุ่มทำงานหนัก / รอฐานข้อมูล</t>
+  </si>
+  <si>
+    <t>1. กดปุ่มบันทึก หรือส่งแบบฟอร์ม</t>
+  </si>
+  <si>
+    <t>ปุ่มจะแสดงสถานะ Loading Spinner และโดน Disable เพื่อป้องกันกดซ้ำ</t>
+  </si>
+  <si>
+    <t>Interactive Element Overlay</t>
+  </si>
+  <si>
+    <t>ชี้ Tooltip หรือคลิกเปิดปุ่ม Dropdown</t>
+  </si>
+  <si>
+    <t>1. ลองชี้เปิด Tooltip บนตารางส่วนต่างๆ</t>
+  </si>
+  <si>
+    <t>องค์ประกอบลอยตัวต้องโชว์เต็มบนสุด (Z-Index ถูกต้อง) ไม่มีอันอื่นมาซ้อนทับ</t>
+  </si>
+  <si>
+    <t>สีข้อความถูกปรับให้สว่างเพื่อให้มองเห็นได้ชัดเจนบนสีกราฟิกมืดทึบ</t>
+  </si>
+  <si>
+    <t>1. เดินดูเมนูต่างๆ ทั้ง Sidebar และกล่องค้นหา</t>
+  </si>
+  <si>
+    <t>ระบบปรับเป็นโหมดมืด (Dark Theme)</t>
+  </si>
+  <si>
+    <t>Dark Mode Display</t>
+  </si>
+  <si>
+    <t>Color Contrast Check</t>
+  </si>
+  <si>
+    <t>1. ตรวจสอบความเข้มของสีตัวอักษรและปุ่มต่างๆ เทียบกับสีพื้นหลัง</t>
+  </si>
+  <si>
+    <t>สบายตาผ่านเกณฑ์ Contrast Ratio ไม่กลืนไปกับพื้นหลังตาม Design System</t>
   </si>
 </sst>
 </file>
@@ -1296,7 +1278,7 @@
     <col min="1" max="1" width="6.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="67.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="77.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -2366,22 +2348,22 @@
         <v>72</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>240</v>
+        <v>31</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2389,22 +2371,22 @@
         <v>73</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="F48" s="3" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2412,42 +2394,42 @@
         <v>74</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="C49" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="E49" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>250</v>
-      </c>
       <c r="D50" s="5" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>77</v>
@@ -2458,19 +2440,19 @@
         <v>76</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>77</v>
